--- a/flare-pwr/SMR_Case/CaseLBLOCA_hot_in.xlsx
+++ b/flare-pwr/SMR_Case/CaseLBLOCA_hot_in.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/FLARE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/flare-pwr/SMR_Case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_6139511B15499A5FE23B44B55F0616FC86E87255" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8DA3634-9618-4104-9A10-5421574F19F1}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_6139511B15499A5FE23B44B55F0616FC86E87255" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80E396F9-86B5-4408-9C0C-0BDC350670AD}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="-10860" windowWidth="19080" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="-11610" windowWidth="16665" windowHeight="9765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CaseLBLOCA_hot_in" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t># CaseLBLOCA_hot: Hot-leg LOCA: steam Dittus-Boelter throughout post-CHF</t>
   </si>
@@ -248,9 +248,6 @@
     <t># NOTBADTRAD Dose Screening</t>
   </si>
   <si>
-    <t>nbt_containment_volume_ft3 = 2.74e6</t>
-  </si>
-  <si>
     <t>nbt_leak_rate_frac_per_day = 0.001</t>
   </si>
   <si>
@@ -263,46 +260,58 @@
     <t>nbt_spray_stop_hr = 24.0</t>
   </si>
   <si>
-    <t>nbt_wind_speed_m_s = 1.0</t>
-  </si>
-  <si>
     <t>nbt_stability_class = "F"</t>
   </si>
   <si>
     <t>nbt_release_height_m = 0.0</t>
   </si>
   <si>
-    <t>nbt_distance_eab_m = 914.0</t>
-  </si>
-  <si>
-    <t>nbt_distance_lpz_m = 4800.0</t>
-  </si>
-  <si>
     <t>nbt_distance_cr_intake_m = 100.0</t>
   </si>
   <si>
     <t>nbt_cr_flow_cfm = 100.0</t>
   </si>
   <si>
-    <t>nbt_cr_volume_ft3 = 20000.0</t>
-  </si>
-  <si>
     <t>nbt_cr_filter_on = True</t>
   </si>
   <si>
-    <t>nbt_end_time_hr = 24.0</t>
-  </si>
-  <si>
     <t>nbt_breathing_rate_m3_s = 3.47e-4</t>
   </si>
   <si>
-    <t>nbt_release_duration_hr = 1.8    # RG 1.183 LBLOCA default</t>
-  </si>
-  <si>
     <t>diameter_break = 0.20   # 0.20 m hot-leg double-ended guillotine break</t>
   </si>
   <si>
     <t>trip_P_lo_kPa = 13338                # 90% desgin</t>
+  </si>
+  <si>
+    <t>nbt_cr_volume_ft3 = 10000.0</t>
+  </si>
+  <si>
+    <t>nbt_distance_eab_m = 335.0    #</t>
+  </si>
+  <si>
+    <t>nbt_distance_lpz_m = 1610.0    # ~3 miles</t>
+  </si>
+  <si>
+    <t>nbt_eab_integration_hr = 2.0</t>
+  </si>
+  <si>
+    <t>nbt_lpz_integration_hr = 8.0    # nbt_end_time_hr = 30*24.0    # dose integration end time [hr]</t>
+  </si>
+  <si>
+    <t>nbt_wind_speed_m_s = 0.33</t>
+  </si>
+  <si>
+    <t>nbt_gap_release_duration_hr = 0.5</t>
+  </si>
+  <si>
+    <t>nbt_early_iv_duration_hr = 1.3</t>
+  </si>
+  <si>
+    <t>nbt_burnup_gwdmtu = 51    # 51 GWd/MTU e.g., CRN ESPA (SSAR Sec. 15.2, ML19030A354)</t>
+  </si>
+  <si>
+    <t>nbt_containment_volume_ft3 = 450000.0</t>
   </si>
 </sst>
 </file>
@@ -656,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q695"/>
+  <dimension ref="A1:Q699"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -952,7 +961,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F35" s="4"/>
       <c r="I35" s="4"/>
@@ -1081,7 +1090,7 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
@@ -1195,206 +1204,155 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>72</v>
+      </c>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>73</v>
       </c>
-      <c r="F80" s="4"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>74</v>
       </c>
-      <c r="F81" s="4"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>88</v>
+      </c>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>75</v>
       </c>
-      <c r="F82" s="4"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>76</v>
       </c>
-      <c r="F83" s="4"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>77</v>
       </c>
-      <c r="F84" s="4"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>78</v>
       </c>
-      <c r="F85" s="4"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>79</v>
-      </c>
-      <c r="F86" s="4"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>80</v>
-      </c>
-      <c r="F87" s="4"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>81</v>
-      </c>
-      <c r="F88" s="4"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>82</v>
-      </c>
       <c r="F89" s="4"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>83</v>
       </c>
       <c r="F90" s="4"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F91" s="4"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F92" s="4"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F93" s="4"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F94" s="4"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>91</v>
+      </c>
       <c r="F95" s="4"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>89</v>
+      </c>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>90</v>
+      </c>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>62</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B100" t="s">
         <v>55</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C100" t="s">
         <v>56</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D100" t="s">
         <v>57</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E100" t="s">
         <v>64</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F100" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J96" s="4"/>
-      <c r="L96" s="2"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>0</v>
-      </c>
-      <c r="B97" s="4">
-        <v>0</v>
-      </c>
-      <c r="C97" s="4">
-        <v>0</v>
-      </c>
-      <c r="D97" s="4">
-        <v>0</v>
-      </c>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="L97" s="2"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>0.50189850000000003</v>
-      </c>
-      <c r="B98" s="4">
-        <v>0</v>
-      </c>
-      <c r="C98" s="4">
-        <v>0</v>
-      </c>
-      <c r="D98" s="4">
-        <v>0</v>
-      </c>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="L98" s="2"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>1.0018990000000001</v>
-      </c>
-      <c r="B99" s="4">
-        <v>0</v>
-      </c>
-      <c r="C99" s="4">
-        <v>0</v>
-      </c>
-      <c r="D99" s="4">
-        <v>0</v>
-      </c>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="L99" s="2"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>1.5018990000000001</v>
-      </c>
-      <c r="B100" s="4">
-        <v>0</v>
-      </c>
-      <c r="C100" s="4">
-        <v>0</v>
-      </c>
-      <c r="D100" s="4">
-        <v>0</v>
-      </c>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
       <c r="J100" s="4"/>
       <c r="L100" s="2"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>2.0018989999999999</v>
+        <v>0</v>
       </c>
       <c r="B101" s="4">
         <v>0</v>
@@ -1412,7 +1370,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>2.5018989999999999</v>
+        <v>0.50189850000000003</v>
       </c>
       <c r="B102" s="4">
         <v>0</v>
@@ -1430,7 +1388,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>3.0018989999999999</v>
+        <v>1.0018990000000001</v>
       </c>
       <c r="B103" s="4">
         <v>0</v>
@@ -1448,7 +1406,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>3.5018989999999999</v>
+        <v>1.5018990000000001</v>
       </c>
       <c r="B104" s="4">
         <v>0</v>
@@ -1466,7 +1424,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>4.0018979999999997</v>
+        <v>2.0018989999999999</v>
       </c>
       <c r="B105" s="4">
         <v>0</v>
@@ -1484,7 +1442,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>4.5018979999999997</v>
+        <v>2.5018989999999999</v>
       </c>
       <c r="B106" s="4">
         <v>0</v>
@@ -1502,7 +1460,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>5.0018979999999997</v>
+        <v>3.0018989999999999</v>
       </c>
       <c r="B107" s="4">
         <v>0</v>
@@ -1520,7 +1478,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>5.5018979999999997</v>
+        <v>3.5018989999999999</v>
       </c>
       <c r="B108" s="4">
         <v>0</v>
@@ -1538,7 +1496,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>6.0018979999999997</v>
+        <v>4.0018979999999997</v>
       </c>
       <c r="B109" s="4">
         <v>0</v>
@@ -1556,7 +1514,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>6.5018979999999997</v>
+        <v>4.5018979999999997</v>
       </c>
       <c r="B110" s="4">
         <v>0</v>
@@ -1574,7 +1532,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>7.0018979999999997</v>
+        <v>5.0018979999999997</v>
       </c>
       <c r="B111" s="4">
         <v>0</v>
@@ -1592,7 +1550,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>7.5018979999999997</v>
+        <v>5.5018979999999997</v>
       </c>
       <c r="B112" s="4">
         <v>0</v>
@@ -1610,7 +1568,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>8.0018989999999999</v>
+        <v>6.0018979999999997</v>
       </c>
       <c r="B113" s="4">
         <v>0</v>
@@ -1628,7 +1586,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>8.5018989999999999</v>
+        <v>6.5018979999999997</v>
       </c>
       <c r="B114" s="4">
         <v>0</v>
@@ -1646,7 +1604,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>9.0018989999999999</v>
+        <v>7.0018979999999997</v>
       </c>
       <c r="B115" s="4">
         <v>0</v>
@@ -1664,7 +1622,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>9.5018989999999999</v>
+        <v>7.5018979999999997</v>
       </c>
       <c r="B116" s="4">
         <v>0</v>
@@ -1682,7 +1640,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>10.001899999999999</v>
+        <v>8.0018989999999999</v>
       </c>
       <c r="B117" s="4">
         <v>0</v>
@@ -1700,7 +1658,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>10.501899999999999</v>
+        <v>8.5018989999999999</v>
       </c>
       <c r="B118" s="4">
         <v>0</v>
@@ -1718,7 +1676,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>11.001899999999999</v>
+        <v>9.0018989999999999</v>
       </c>
       <c r="B119" s="4">
         <v>0</v>
@@ -1736,7 +1694,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>11.501899999999999</v>
+        <v>9.5018989999999999</v>
       </c>
       <c r="B120" s="4">
         <v>0</v>
@@ -1754,7 +1712,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>12.001899999999999</v>
+        <v>10.001899999999999</v>
       </c>
       <c r="B121" s="4">
         <v>0</v>
@@ -1772,7 +1730,7 @@
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>12.501899999999999</v>
+        <v>10.501899999999999</v>
       </c>
       <c r="B122" s="4">
         <v>0</v>
@@ -1790,7 +1748,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>13.001899999999999</v>
+        <v>11.001899999999999</v>
       </c>
       <c r="B123" s="4">
         <v>0</v>
@@ -1808,7 +1766,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>13.501899999999999</v>
+        <v>11.501899999999999</v>
       </c>
       <c r="B124" s="4">
         <v>0</v>
@@ -1826,7 +1784,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>14.001899999999999</v>
+        <v>12.001899999999999</v>
       </c>
       <c r="B125" s="4">
         <v>0</v>
@@ -1844,7 +1802,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>14.501899999999999</v>
+        <v>12.501899999999999</v>
       </c>
       <c r="B126" s="4">
         <v>0</v>
@@ -1862,7 +1820,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>15.0009</v>
+        <v>13.001899999999999</v>
       </c>
       <c r="B127" s="4">
         <v>0</v>
@@ -1880,7 +1838,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>16.001449999999998</v>
+        <v>13.501899999999999</v>
       </c>
       <c r="B128" s="4">
         <v>0</v>
@@ -1898,7 +1856,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>17.00123</v>
+        <v>14.001899999999999</v>
       </c>
       <c r="B129" s="4">
         <v>0</v>
@@ -1916,7 +1874,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>18.001429999999999</v>
+        <v>14.501899999999999</v>
       </c>
       <c r="B130" s="4">
         <v>0</v>
@@ -1934,7 +1892,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>19.002050000000001</v>
+        <v>15.0009</v>
       </c>
       <c r="B131" s="4">
         <v>0</v>
@@ -1952,7 +1910,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>20.001339999999999</v>
+        <v>16.001449999999998</v>
       </c>
       <c r="B132" s="4">
         <v>0</v>
@@ -1970,7 +1928,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>21.00207</v>
+        <v>17.00123</v>
       </c>
       <c r="B133" s="4">
         <v>0</v>
@@ -1988,7 +1946,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>22.001460000000002</v>
+        <v>18.001429999999999</v>
       </c>
       <c r="B134" s="4">
         <v>0</v>
@@ -2006,7 +1964,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>23.001750000000001</v>
+        <v>19.002050000000001</v>
       </c>
       <c r="B135" s="4">
         <v>0</v>
@@ -2024,7 +1982,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>24.002279999999999</v>
+        <v>20.001339999999999</v>
       </c>
       <c r="B136" s="4">
         <v>0</v>
@@ -2042,7 +2000,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>25.002549999999999</v>
+        <v>21.00207</v>
       </c>
       <c r="B137" s="4">
         <v>0</v>
@@ -2060,7 +2018,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>26.001860000000001</v>
+        <v>22.001460000000002</v>
       </c>
       <c r="B138" s="4">
         <v>0</v>
@@ -2078,7 +2036,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>27.002220000000001</v>
+        <v>23.001750000000001</v>
       </c>
       <c r="B139" s="4">
         <v>0</v>
@@ -2096,7 +2054,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>28.001290000000001</v>
+        <v>24.002279999999999</v>
       </c>
       <c r="B140" s="4">
         <v>0</v>
@@ -2114,7 +2072,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>29.00226</v>
+        <v>25.002549999999999</v>
       </c>
       <c r="B141" s="4">
         <v>0</v>
@@ -2132,7 +2090,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>30.00151</v>
+        <v>26.001860000000001</v>
       </c>
       <c r="B142" s="4">
         <v>0</v>
@@ -2146,10 +2104,11 @@
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="J142" s="4"/>
+      <c r="L142" s="2"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>31.002330000000001</v>
+        <v>27.002220000000001</v>
       </c>
       <c r="B143" s="4">
         <v>0</v>
@@ -2162,11 +2121,12 @@
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
+      <c r="J143" s="4"/>
       <c r="L143" s="2"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>32.002200000000002</v>
+        <v>28.001290000000001</v>
       </c>
       <c r="B144" s="4">
         <v>0</v>
@@ -2179,10 +2139,12 @@
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J144" s="4"/>
+      <c r="L144" s="2"/>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>33.001280000000001</v>
+        <v>29.00226</v>
       </c>
       <c r="B145" s="4">
         <v>0</v>
@@ -2195,10 +2157,12 @@
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J145" s="4"/>
+      <c r="L145" s="2"/>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>34.001510000000003</v>
+        <v>30.00151</v>
       </c>
       <c r="B146" s="4">
         <v>0</v>
@@ -2211,10 +2175,11 @@
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J146" s="4"/>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>35.002409999999998</v>
+        <v>31.002330000000001</v>
       </c>
       <c r="B147" s="4">
         <v>0</v>
@@ -2227,10 +2192,11 @@
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L147" s="2"/>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>36.001139999999999</v>
+        <v>32.002200000000002</v>
       </c>
       <c r="B148" s="4">
         <v>0</v>
@@ -2244,9 +2210,9 @@
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>37.001289999999997</v>
+        <v>33.001280000000001</v>
       </c>
       <c r="B149" s="4">
         <v>0</v>
@@ -2260,9 +2226,9 @@
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>38.001910000000002</v>
+        <v>34.001510000000003</v>
       </c>
       <c r="B150" s="4">
         <v>0</v>
@@ -2276,9 +2242,9 @@
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>39.00264</v>
+        <v>35.002409999999998</v>
       </c>
       <c r="B151" s="4">
         <v>0</v>
@@ -2292,9 +2258,9 @@
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>40.002310000000001</v>
+        <v>36.001139999999999</v>
       </c>
       <c r="B152" s="4">
         <v>0</v>
@@ -2308,9 +2274,9 @@
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>41.002189999999999</v>
+        <v>37.001289999999997</v>
       </c>
       <c r="B153" s="4">
         <v>0</v>
@@ -2324,9 +2290,9 @@
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>42.002339999999997</v>
+        <v>38.001910000000002</v>
       </c>
       <c r="B154" s="4">
         <v>0</v>
@@ -2340,9 +2306,9 @@
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>43.001480000000001</v>
+        <v>39.00264</v>
       </c>
       <c r="B155" s="4">
         <v>0</v>
@@ -2356,9 +2322,9 @@
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>44.000900000000001</v>
+        <v>40.002310000000001</v>
       </c>
       <c r="B156" s="4">
         <v>0</v>
@@ -2372,9 +2338,9 @@
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>45.000900000000001</v>
+        <v>41.002189999999999</v>
       </c>
       <c r="B157" s="4">
         <v>0</v>
@@ -2388,9 +2354,9 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>46.003019999999999</v>
+        <v>42.002339999999997</v>
       </c>
       <c r="B158" s="4">
         <v>0</v>
@@ -2404,9 +2370,9 @@
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>47.001150000000003</v>
+        <v>43.001480000000001</v>
       </c>
       <c r="B159" s="4">
         <v>0</v>
@@ -2420,9 +2386,9 @@
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>48.001060000000003</v>
+        <v>44.000900000000001</v>
       </c>
       <c r="B160" s="4">
         <v>0</v>
@@ -2438,7 +2404,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>49.001530000000002</v>
+        <v>45.000900000000001</v>
       </c>
       <c r="B161" s="4">
         <v>0</v>
@@ -2454,7 +2420,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>50.00215</v>
+        <v>46.003019999999999</v>
       </c>
       <c r="B162" s="4">
         <v>0</v>
@@ -2470,7 +2436,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>51.002270000000003</v>
+        <v>47.001150000000003</v>
       </c>
       <c r="B163" s="4">
         <v>0</v>
@@ -2486,7 +2452,7 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>52.002360000000003</v>
+        <v>48.001060000000003</v>
       </c>
       <c r="B164" s="4">
         <v>0</v>
@@ -2502,7 +2468,7 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>53.001339999999999</v>
+        <v>49.001530000000002</v>
       </c>
       <c r="B165" s="4">
         <v>0</v>
@@ -2518,7 +2484,7 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>54.002800000000001</v>
+        <v>50.00215</v>
       </c>
       <c r="B166" s="4">
         <v>0</v>
@@ -2534,7 +2500,7 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>55.001890000000003</v>
+        <v>51.002270000000003</v>
       </c>
       <c r="B167" s="4">
         <v>0</v>
@@ -2550,7 +2516,7 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>56.002189999999999</v>
+        <v>52.002360000000003</v>
       </c>
       <c r="B168" s="4">
         <v>0</v>
@@ -2566,7 +2532,7 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>57.002589999999998</v>
+        <v>53.001339999999999</v>
       </c>
       <c r="B169" s="4">
         <v>0</v>
@@ -2582,7 +2548,7 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>58.002719999999997</v>
+        <v>54.002800000000001</v>
       </c>
       <c r="B170" s="4">
         <v>0</v>
@@ -2598,7 +2564,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>59.00132</v>
+        <v>55.001890000000003</v>
       </c>
       <c r="B171" s="4">
         <v>0</v>
@@ -2614,7 +2580,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>60.002429999999997</v>
+        <v>56.002189999999999</v>
       </c>
       <c r="B172" s="4">
         <v>0</v>
@@ -2630,7 +2596,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>61.003120000000003</v>
+        <v>57.002589999999998</v>
       </c>
       <c r="B173" s="4">
         <v>0</v>
@@ -2646,7 +2612,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>62.002960000000002</v>
+        <v>58.002719999999997</v>
       </c>
       <c r="B174" s="4">
         <v>0</v>
@@ -2662,7 +2628,7 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>63.00141</v>
+        <v>59.00132</v>
       </c>
       <c r="B175" s="4">
         <v>0</v>
@@ -2678,7 +2644,7 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>64.001249999999999</v>
+        <v>60.002429999999997</v>
       </c>
       <c r="B176" s="4">
         <v>0</v>
@@ -2694,7 +2660,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>65.001559999999998</v>
+        <v>61.003120000000003</v>
       </c>
       <c r="B177" s="4">
         <v>0</v>
@@ -2710,7 +2676,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>66.001350000000002</v>
+        <v>62.002960000000002</v>
       </c>
       <c r="B178" s="4">
         <v>0</v>
@@ -2726,7 +2692,7 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>67.001750000000001</v>
+        <v>63.00141</v>
       </c>
       <c r="B179" s="4">
         <v>0</v>
@@ -2742,7 +2708,7 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>68.00215</v>
+        <v>64.001249999999999</v>
       </c>
       <c r="B180" s="4">
         <v>0</v>
@@ -2758,7 +2724,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>69.002030000000005</v>
+        <v>65.001559999999998</v>
       </c>
       <c r="B181" s="4">
         <v>0</v>
@@ -2774,7 +2740,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>70.00179</v>
+        <v>66.001350000000002</v>
       </c>
       <c r="B182" s="4">
         <v>0</v>
@@ -2790,7 +2756,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>71.001850000000005</v>
+        <v>67.001750000000001</v>
       </c>
       <c r="B183" s="4">
         <v>0</v>
@@ -2806,7 +2772,7 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>72.002319999999997</v>
+        <v>68.00215</v>
       </c>
       <c r="B184" s="4">
         <v>0</v>
@@ -2822,7 +2788,7 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>73.001509999999996</v>
+        <v>69.002030000000005</v>
       </c>
       <c r="B185" s="4">
         <v>0</v>
@@ -2838,7 +2804,7 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>74.002219999999994</v>
+        <v>70.00179</v>
       </c>
       <c r="B186" s="4">
         <v>0</v>
@@ -2854,7 +2820,7 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>75.001559999999998</v>
+        <v>71.001850000000005</v>
       </c>
       <c r="B187" s="4">
         <v>0</v>
@@ -2870,7 +2836,7 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>76.001050000000006</v>
+        <v>72.002319999999997</v>
       </c>
       <c r="B188" s="4">
         <v>0</v>
@@ -2886,7 +2852,7 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>77.002170000000007</v>
+        <v>73.001509999999996</v>
       </c>
       <c r="B189" s="4">
         <v>0</v>
@@ -2902,7 +2868,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>78.002430000000004</v>
+        <v>74.002219999999994</v>
       </c>
       <c r="B190" s="4">
         <v>0</v>
@@ -2918,7 +2884,7 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>79.002489999999995</v>
+        <v>75.001559999999998</v>
       </c>
       <c r="B191" s="4">
         <v>0</v>
@@ -2934,7 +2900,7 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>80.001570000000001</v>
+        <v>76.001050000000006</v>
       </c>
       <c r="B192" s="4">
         <v>0</v>
@@ -2950,7 +2916,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>81.001429999999999</v>
+        <v>77.002170000000007</v>
       </c>
       <c r="B193" s="4">
         <v>0</v>
@@ -2966,7 +2932,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>82.002300000000005</v>
+        <v>78.002430000000004</v>
       </c>
       <c r="B194" s="4">
         <v>0</v>
@@ -2982,7 +2948,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>83.001649999999998</v>
+        <v>79.002489999999995</v>
       </c>
       <c r="B195" s="4">
         <v>0</v>
@@ -2998,7 +2964,7 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>84.001949999999994</v>
+        <v>80.001570000000001</v>
       </c>
       <c r="B196" s="4">
         <v>0</v>
@@ -3014,7 +2980,7 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>85.002120000000005</v>
+        <v>81.001429999999999</v>
       </c>
       <c r="B197" s="4">
         <v>0</v>
@@ -3030,7 +2996,7 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>86.000979999999998</v>
+        <v>82.002300000000005</v>
       </c>
       <c r="B198" s="4">
         <v>0</v>
@@ -3046,7 +3012,7 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>87.001890000000003</v>
+        <v>83.001649999999998</v>
       </c>
       <c r="B199" s="4">
         <v>0</v>
@@ -3062,7 +3028,7 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>88.001289999999997</v>
+        <v>84.001949999999994</v>
       </c>
       <c r="B200" s="4">
         <v>0</v>
@@ -3078,7 +3044,7 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>89.001540000000006</v>
+        <v>85.002120000000005</v>
       </c>
       <c r="B201" s="4">
         <v>0</v>
@@ -3094,7 +3060,7 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>90.001869999999997</v>
+        <v>86.000979999999998</v>
       </c>
       <c r="B202" s="4">
         <v>0</v>
@@ -3110,7 +3076,7 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>91.001440000000002</v>
+        <v>87.001890000000003</v>
       </c>
       <c r="B203" s="4">
         <v>0</v>
@@ -3126,7 +3092,7 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>92.001040000000003</v>
+        <v>88.001289999999997</v>
       </c>
       <c r="B204" s="4">
         <v>0</v>
@@ -3142,7 +3108,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>93.001400000000004</v>
+        <v>89.001540000000006</v>
       </c>
       <c r="B205" s="4">
         <v>0</v>
@@ -3158,7 +3124,7 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>94.001310000000004</v>
+        <v>90.001869999999997</v>
       </c>
       <c r="B206" s="4">
         <v>0</v>
@@ -3174,7 +3140,7 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>95.00197</v>
+        <v>91.001440000000002</v>
       </c>
       <c r="B207" s="4">
         <v>0</v>
@@ -3190,7 +3156,7 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>96.002009999999999</v>
+        <v>92.001040000000003</v>
       </c>
       <c r="B208" s="4">
         <v>0</v>
@@ -3206,7 +3172,7 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>97.0017</v>
+        <v>93.001400000000004</v>
       </c>
       <c r="B209" s="4">
         <v>0</v>
@@ -3222,7 +3188,7 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>98.001540000000006</v>
+        <v>94.001310000000004</v>
       </c>
       <c r="B210" s="4">
         <v>0</v>
@@ -3238,7 +3204,7 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>99.001850000000005</v>
+        <v>95.00197</v>
       </c>
       <c r="B211" s="4">
         <v>0</v>
@@ -3254,7 +3220,7 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>100.00109999999999</v>
+        <v>96.002009999999999</v>
       </c>
       <c r="B212" s="4">
         <v>0</v>
@@ -3270,7 +3236,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>110.0013</v>
+        <v>97.0017</v>
       </c>
       <c r="B213" s="4">
         <v>0</v>
@@ -3286,7 +3252,7 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>120.0018</v>
+        <v>98.001540000000006</v>
       </c>
       <c r="B214" s="4">
         <v>0</v>
@@ -3302,7 +3268,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>130.00210000000001</v>
+        <v>99.001850000000005</v>
       </c>
       <c r="B215" s="4">
         <v>0</v>
@@ -3318,7 +3284,7 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>140.00139999999999</v>
+        <v>100.00109999999999</v>
       </c>
       <c r="B216" s="4">
         <v>0</v>
@@ -3334,7 +3300,7 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>150.00190000000001</v>
+        <v>110.0013</v>
       </c>
       <c r="B217" s="4">
         <v>0</v>
@@ -3350,7 +3316,7 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>160.00219999999999</v>
+        <v>120.0018</v>
       </c>
       <c r="B218" s="4">
         <v>0</v>
@@ -3366,7 +3332,7 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>170.00219999999999</v>
+        <v>130.00210000000001</v>
       </c>
       <c r="B219" s="4">
         <v>0</v>
@@ -3382,7 +3348,7 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>180.0017</v>
+        <v>140.00139999999999</v>
       </c>
       <c r="B220" s="4">
         <v>0</v>
@@ -3398,7 +3364,7 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>190.00190000000001</v>
+        <v>150.00190000000001</v>
       </c>
       <c r="B221" s="4">
         <v>0</v>
@@ -3414,7 +3380,7 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>200.00190000000001</v>
+        <v>160.00219999999999</v>
       </c>
       <c r="B222" s="4">
         <v>0</v>
@@ -3430,7 +3396,7 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>210.00120000000001</v>
+        <v>170.00219999999999</v>
       </c>
       <c r="B223" s="4">
         <v>0</v>
@@ -3446,7 +3412,7 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>220.00120000000001</v>
+        <v>180.0017</v>
       </c>
       <c r="B224" s="4">
         <v>0</v>
@@ -3462,7 +3428,7 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>230.0017</v>
+        <v>190.00190000000001</v>
       </c>
       <c r="B225" s="4">
         <v>0</v>
@@ -3478,7 +3444,7 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>240.00200000000001</v>
+        <v>200.00190000000001</v>
       </c>
       <c r="B226" s="4">
         <v>0</v>
@@ -3494,7 +3460,7 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>250.00129999999999</v>
+        <v>210.00120000000001</v>
       </c>
       <c r="B227" s="4">
         <v>0</v>
@@ -3510,7 +3476,7 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>260.0018</v>
+        <v>220.00120000000001</v>
       </c>
       <c r="B228" s="4">
         <v>0</v>
@@ -3526,7 +3492,7 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>270.00119999999998</v>
+        <v>230.0017</v>
       </c>
       <c r="B229" s="4">
         <v>0</v>
@@ -3542,7 +3508,7 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>280.00170000000003</v>
+        <v>240.00200000000001</v>
       </c>
       <c r="B230" s="4">
         <v>0</v>
@@ -3558,7 +3524,7 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>290.00150000000002</v>
+        <v>250.00129999999999</v>
       </c>
       <c r="B231" s="4">
         <v>0</v>
@@ -3574,7 +3540,7 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>300.0016</v>
+        <v>260.0018</v>
       </c>
       <c r="B232" s="4">
         <v>0</v>
@@ -3590,7 +3556,7 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>310.00189999999998</v>
+        <v>270.00119999999998</v>
       </c>
       <c r="B233" s="4">
         <v>0</v>
@@ -3606,7 +3572,7 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>320.00170000000003</v>
+        <v>280.00170000000003</v>
       </c>
       <c r="B234" s="4">
         <v>0</v>
@@ -3622,7 +3588,7 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>330.00150000000002</v>
+        <v>290.00150000000002</v>
       </c>
       <c r="B235" s="4">
         <v>0</v>
@@ -3638,7 +3604,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>340.00189999999998</v>
+        <v>300.0016</v>
       </c>
       <c r="B236" s="4">
         <v>0</v>
@@ -3654,7 +3620,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>350.00170000000003</v>
+        <v>310.00189999999998</v>
       </c>
       <c r="B237" s="4">
         <v>0</v>
@@ -3670,7 +3636,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>360.00150000000002</v>
+        <v>320.00170000000003</v>
       </c>
       <c r="B238" s="4">
         <v>0</v>
@@ -3686,7 +3652,7 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>370.00150000000002</v>
+        <v>330.00150000000002</v>
       </c>
       <c r="B239" s="4">
         <v>0</v>
@@ -3702,7 +3668,7 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>380.00139999999999</v>
+        <v>340.00189999999998</v>
       </c>
       <c r="B240" s="4">
         <v>0</v>
@@ -3718,7 +3684,7 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>390.00200000000001</v>
+        <v>350.00170000000003</v>
       </c>
       <c r="B241" s="4">
         <v>0</v>
@@ -3734,7 +3700,7 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>400.00200000000001</v>
+        <v>360.00150000000002</v>
       </c>
       <c r="B242" s="4">
         <v>0</v>
@@ -3750,7 +3716,7 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>410.0016</v>
+        <v>370.00150000000002</v>
       </c>
       <c r="B243" s="4">
         <v>0</v>
@@ -3766,7 +3732,7 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>420.0016</v>
+        <v>380.00139999999999</v>
       </c>
       <c r="B244" s="4">
         <v>0</v>
@@ -3782,7 +3748,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>430.00200000000001</v>
+        <v>390.00200000000001</v>
       </c>
       <c r="B245" s="4">
         <v>0</v>
@@ -3798,7 +3764,7 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>440.00189999999998</v>
+        <v>400.00200000000001</v>
       </c>
       <c r="B246" s="4">
         <v>0</v>
@@ -3814,7 +3780,7 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>450.00170000000003</v>
+        <v>410.0016</v>
       </c>
       <c r="B247" s="4">
         <v>0</v>
@@ -3830,7 +3796,7 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>460.0018</v>
+        <v>420.0016</v>
       </c>
       <c r="B248" s="4">
         <v>0</v>
@@ -3846,7 +3812,7 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>470.00130000000001</v>
+        <v>430.00200000000001</v>
       </c>
       <c r="B249" s="4">
         <v>0</v>
@@ -3862,7 +3828,7 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>480.00150000000002</v>
+        <v>440.00189999999998</v>
       </c>
       <c r="B250" s="4">
         <v>0</v>
@@ -3878,7 +3844,7 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>490.0016</v>
+        <v>450.00170000000003</v>
       </c>
       <c r="B251" s="4">
         <v>0</v>
@@ -3894,7 +3860,7 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>500.00200000000001</v>
+        <v>460.0018</v>
       </c>
       <c r="B252" s="4">
         <v>0</v>
@@ -3910,7 +3876,7 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>510.0025</v>
+        <v>470.00130000000001</v>
       </c>
       <c r="B253" s="4">
         <v>0</v>
@@ -3926,7 +3892,7 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>520.00199999999995</v>
+        <v>480.00150000000002</v>
       </c>
       <c r="B254" s="4">
         <v>0</v>
@@ -3942,7 +3908,7 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>530.00139999999999</v>
+        <v>490.0016</v>
       </c>
       <c r="B255" s="4">
         <v>0</v>
@@ -3958,7 +3924,7 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>540.00210000000004</v>
+        <v>500.00200000000001</v>
       </c>
       <c r="B256" s="4">
         <v>0</v>
@@ -3974,7 +3940,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>550.0018</v>
+        <v>510.0025</v>
       </c>
       <c r="B257" s="4">
         <v>0</v>
@@ -3990,7 +3956,7 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>560.00220000000002</v>
+        <v>520.00199999999995</v>
       </c>
       <c r="B258" s="4">
         <v>0</v>
@@ -4006,7 +3972,7 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>570.0018</v>
+        <v>530.00139999999999</v>
       </c>
       <c r="B259" s="4">
         <v>0</v>
@@ -4022,7 +3988,7 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>580.00220000000002</v>
+        <v>540.00210000000004</v>
       </c>
       <c r="B260" s="4">
         <v>0</v>
@@ -4038,7 +4004,7 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>590.00130000000001</v>
+        <v>550.0018</v>
       </c>
       <c r="B261" s="4">
         <v>0</v>
@@ -4054,7 +4020,7 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>600.00120000000004</v>
+        <v>560.00220000000002</v>
       </c>
       <c r="B262" s="4">
         <v>0</v>
@@ -4070,7 +4036,7 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>610.00120000000004</v>
+        <v>570.0018</v>
       </c>
       <c r="B263" s="4">
         <v>0</v>
@@ -4086,7 +4052,7 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>620.00130000000001</v>
+        <v>580.00220000000002</v>
       </c>
       <c r="B264" s="4">
         <v>0</v>
@@ -4102,7 +4068,7 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>630.00160000000005</v>
+        <v>590.00130000000001</v>
       </c>
       <c r="B265" s="4">
         <v>0</v>
@@ -4118,7 +4084,7 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>640.00239999999997</v>
+        <v>600.00120000000004</v>
       </c>
       <c r="B266" s="4">
         <v>0</v>
@@ -4134,7 +4100,7 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>650.00229999999999</v>
+        <v>610.00120000000004</v>
       </c>
       <c r="B267" s="4">
         <v>0</v>
@@ -4150,7 +4116,7 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>660.0018</v>
+        <v>620.00130000000001</v>
       </c>
       <c r="B268" s="4">
         <v>0</v>
@@ -4166,7 +4132,7 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>670.00250000000005</v>
+        <v>630.00160000000005</v>
       </c>
       <c r="B269" s="4">
         <v>0</v>
@@ -4182,7 +4148,7 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>680.00120000000004</v>
+        <v>640.00239999999997</v>
       </c>
       <c r="B270" s="4">
         <v>0</v>
@@ -4198,7 +4164,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>690.0018</v>
+        <v>650.00229999999999</v>
       </c>
       <c r="B271" s="4">
         <v>0</v>
@@ -4214,7 +4180,7 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>700.00149999999996</v>
+        <v>660.0018</v>
       </c>
       <c r="B272" s="4">
         <v>0</v>
@@ -4230,7 +4196,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>710.0018</v>
+        <v>670.00250000000005</v>
       </c>
       <c r="B273" s="4">
         <v>0</v>
@@ -4246,7 +4212,7 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>720.00149999999996</v>
+        <v>680.00120000000004</v>
       </c>
       <c r="B274" s="4">
         <v>0</v>
@@ -4262,7 +4228,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>730.00149999999996</v>
+        <v>690.0018</v>
       </c>
       <c r="B275" s="4">
         <v>0</v>
@@ -4278,7 +4244,7 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>740.00239999999997</v>
+        <v>700.00149999999996</v>
       </c>
       <c r="B276" s="4">
         <v>0</v>
@@ -4294,7 +4260,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>750.00239999999997</v>
+        <v>710.0018</v>
       </c>
       <c r="B277" s="4">
         <v>0</v>
@@ -4310,7 +4276,7 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>760.00199999999995</v>
+        <v>720.00149999999996</v>
       </c>
       <c r="B278" s="4">
         <v>0</v>
@@ -4326,7 +4292,7 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>770.00210000000004</v>
+        <v>730.00149999999996</v>
       </c>
       <c r="B279" s="4">
         <v>0</v>
@@ -4342,7 +4308,7 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>780.00160000000005</v>
+        <v>740.00239999999997</v>
       </c>
       <c r="B280" s="4">
         <v>0</v>
@@ -4358,7 +4324,7 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>790.00160000000005</v>
+        <v>750.00239999999997</v>
       </c>
       <c r="B281" s="4">
         <v>0</v>
@@ -4374,7 +4340,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>800.00210000000004</v>
+        <v>760.00199999999995</v>
       </c>
       <c r="B282" s="4">
         <v>0</v>
@@ -4390,7 +4356,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>810.00239999999997</v>
+        <v>770.00210000000004</v>
       </c>
       <c r="B283" s="4">
         <v>0</v>
@@ -4406,7 +4372,7 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>820.00170000000003</v>
+        <v>780.00160000000005</v>
       </c>
       <c r="B284" s="4">
         <v>0</v>
@@ -4422,7 +4388,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>830.00170000000003</v>
+        <v>790.00160000000005</v>
       </c>
       <c r="B285" s="4">
         <v>0</v>
@@ -4438,7 +4404,7 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>840.00199999999995</v>
+        <v>800.00210000000004</v>
       </c>
       <c r="B286" s="4">
         <v>0</v>
@@ -4454,7 +4420,7 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>850.00170000000003</v>
+        <v>810.00239999999997</v>
       </c>
       <c r="B287" s="4">
         <v>0</v>
@@ -4470,7 +4436,7 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>860.00220000000002</v>
+        <v>820.00170000000003</v>
       </c>
       <c r="B288" s="4">
         <v>0</v>
@@ -4486,7 +4452,7 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>870.00220000000002</v>
+        <v>830.00170000000003</v>
       </c>
       <c r="B289" s="4">
         <v>0</v>
@@ -4502,7 +4468,7 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>880.0027</v>
+        <v>840.00199999999995</v>
       </c>
       <c r="B290" s="4">
         <v>0</v>
@@ -4518,7 +4484,7 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>890.00139999999999</v>
+        <v>850.00170000000003</v>
       </c>
       <c r="B291" s="4">
         <v>0</v>
@@ -4534,7 +4500,7 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>900.0018</v>
+        <v>860.00220000000002</v>
       </c>
       <c r="B292" s="4">
         <v>0</v>
@@ -4550,7 +4516,7 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>910.00210000000004</v>
+        <v>870.00220000000002</v>
       </c>
       <c r="B293" s="4">
         <v>0</v>
@@ -4566,7 +4532,7 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>920.00139999999999</v>
+        <v>880.0027</v>
       </c>
       <c r="B294" s="4">
         <v>0</v>
@@ -4582,7 +4548,7 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>930.00199999999995</v>
+        <v>890.00139999999999</v>
       </c>
       <c r="B295" s="4">
         <v>0</v>
@@ -4598,7 +4564,7 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>940.00160000000005</v>
+        <v>900.0018</v>
       </c>
       <c r="B296" s="4">
         <v>0</v>
@@ -4614,7 +4580,7 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>950.00130000000001</v>
+        <v>910.00210000000004</v>
       </c>
       <c r="B297" s="4">
         <v>0</v>
@@ -4630,7 +4596,7 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>960.00210000000004</v>
+        <v>920.00139999999999</v>
       </c>
       <c r="B298" s="4">
         <v>0</v>
@@ -4646,7 +4612,7 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>970.00120000000004</v>
+        <v>930.00199999999995</v>
       </c>
       <c r="B299" s="4">
         <v>0</v>
@@ -4662,7 +4628,7 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>980.0018</v>
+        <v>940.00160000000005</v>
       </c>
       <c r="B300" s="4">
         <v>0</v>
@@ -4678,7 +4644,7 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>990.00220000000002</v>
+        <v>950.00130000000001</v>
       </c>
       <c r="B301" s="4">
         <v>0</v>
@@ -4694,7 +4660,7 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>1000.002</v>
+        <v>960.00210000000004</v>
       </c>
       <c r="B302" s="4">
         <v>0</v>
@@ -4709,125 +4675,161 @@
       <c r="F302" s="4"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B303" s="4"/>
-      <c r="C303" s="4"/>
-      <c r="D303" s="4"/>
+      <c r="A303">
+        <v>970.00120000000004</v>
+      </c>
+      <c r="B303" s="4">
+        <v>0</v>
+      </c>
+      <c r="C303" s="4">
+        <v>0</v>
+      </c>
+      <c r="D303" s="4">
+        <v>0</v>
+      </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B304" s="4"/>
-      <c r="C304" s="4"/>
-      <c r="D304" s="4"/>
+      <c r="A304">
+        <v>980.0018</v>
+      </c>
+      <c r="B304" s="4">
+        <v>0</v>
+      </c>
+      <c r="C304" s="4">
+        <v>0</v>
+      </c>
+      <c r="D304" s="4">
+        <v>0</v>
+      </c>
       <c r="E304" s="4"/>
       <c r="F304" s="4"/>
     </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B305" s="4"/>
-      <c r="C305" s="4"/>
-      <c r="D305" s="4"/>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>990.00220000000002</v>
+      </c>
+      <c r="B305" s="4">
+        <v>0</v>
+      </c>
+      <c r="C305" s="4">
+        <v>0</v>
+      </c>
+      <c r="D305" s="4">
+        <v>0</v>
+      </c>
       <c r="E305" s="4"/>
       <c r="F305" s="4"/>
     </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B306" s="4"/>
-      <c r="C306" s="4"/>
-      <c r="D306" s="4"/>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>1000.002</v>
+      </c>
+      <c r="B306" s="4">
+        <v>0</v>
+      </c>
+      <c r="C306" s="4">
+        <v>0</v>
+      </c>
+      <c r="D306" s="4">
+        <v>0</v>
+      </c>
       <c r="E306" s="4"/>
       <c r="F306" s="4"/>
     </row>
-    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
       <c r="F307" s="4"/>
     </row>
-    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
       <c r="F308" s="4"/>
     </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
       <c r="F309" s="4"/>
     </row>
-    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
       <c r="E310" s="4"/>
       <c r="F310" s="4"/>
     </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
       <c r="F311" s="4"/>
     </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
       <c r="E312" s="4"/>
       <c r="F312" s="4"/>
     </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
       <c r="F313" s="4"/>
     </row>
-    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
       <c r="E314" s="4"/>
       <c r="F314" s="4"/>
     </row>
-    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
       <c r="F315" s="4"/>
     </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
       <c r="E316" s="4"/>
       <c r="F316" s="4"/>
     </row>
-    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
       <c r="F317" s="4"/>
     </row>
-    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
       <c r="F318" s="4"/>
     </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
       <c r="F319" s="4"/>
     </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
@@ -7310,24 +7312,28 @@
       <c r="C674" s="4"/>
       <c r="D674" s="4"/>
       <c r="E674" s="4"/>
+      <c r="F674" s="4"/>
     </row>
     <row r="675" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
       <c r="D675" s="4"/>
       <c r="E675" s="4"/>
+      <c r="F675" s="4"/>
     </row>
     <row r="676" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
       <c r="D676" s="4"/>
       <c r="E676" s="4"/>
+      <c r="F676" s="4"/>
     </row>
     <row r="677" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
       <c r="D677" s="4"/>
       <c r="E677" s="4"/>
+      <c r="F677" s="4"/>
     </row>
     <row r="678" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B678" s="4"/>
@@ -7437,6 +7443,30 @@
       <c r="D695" s="4"/>
       <c r="E695" s="4"/>
     </row>
+    <row r="696" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B696" s="4"/>
+      <c r="C696" s="4"/>
+      <c r="D696" s="4"/>
+      <c r="E696" s="4"/>
+    </row>
+    <row r="697" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B697" s="4"/>
+      <c r="C697" s="4"/>
+      <c r="D697" s="4"/>
+      <c r="E697" s="4"/>
+    </row>
+    <row r="698" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B698" s="4"/>
+      <c r="C698" s="4"/>
+      <c r="D698" s="4"/>
+      <c r="E698" s="4"/>
+    </row>
+    <row r="699" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B699" s="4"/>
+      <c r="C699" s="4"/>
+      <c r="D699" s="4"/>
+      <c r="E699" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
